--- a/study_case_model/unit_networks/scenario_variables/price_scenarios111.xlsx
+++ b/study_case_model/unit_networks/scenario_variables/price_scenarios111.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,10 +458,52 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.97786141248077</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>25.62567570941777</v>
+      <c r="C3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" t="n">
+        <v>26.49351099259378</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D4" t="n">
+        <v>23.00708937390168</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" t="n">
+        <v>27.78772767425982</v>
       </c>
     </row>
   </sheetData>
